--- a/InputData/elec/RM/Reserve Margin.xlsx
+++ b/InputData/elec/RM/Reserve Margin.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robbie\Dropbox (Energy InNovation)\My Documents\Policy Solutions Project\India\India EPS\InputData UPDATE FOR INDIA\elec\RM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\RM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>RM Reserve Margin</t>
   </si>
@@ -28,19 +28,34 @@
     <t>Source:</t>
   </si>
   <si>
+    <t xml:space="preserve">North American Electrict Reliability Coorporation </t>
+  </si>
+  <si>
+    <t>http://www.nerc.com/pa/RAPA/ra/Reliability%20Assessments%20DL/2015_Summer_Reliability_Assessment.pdf</t>
+  </si>
+  <si>
+    <t>p.3, Table 1: Projected Demand, Resources, and Planning Reserve Margins, NERC Reference Margin Level (%)</t>
+  </si>
+  <si>
+    <t>2015 Summer Reliability Assessment</t>
+  </si>
+  <si>
     <t>Reserve Margin</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">India's actual reserve margin is very high, on the order of 50-70%, so we </t>
-  </si>
-  <si>
-    <t>default to a normal, "good practice" reserve margin of 15%.</t>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The reserve margin (difference between the total generation available and the forecasted peak demand) in the U.S. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataset doesn't vary by year, but the RM Reserve Margin variable is a time series to support countries that project </t>
+  </si>
+  <si>
+    <t>changes in future reserve margin by year.</t>
+  </si>
+  <si>
+    <t>(dimensionless)</t>
   </si>
 </sst>
 </file>
@@ -395,41 +410,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B4" s="2">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -444,12 +478,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
       <c r="B1">
         <v>2015</v>
       </c>
@@ -559,117 +596,117 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="C2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="D2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="E2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="F2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="G2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="H2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="I2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="J2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="K2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="L2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="M2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="N2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="O2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="P2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="R2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="S2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="T2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="U2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="V2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="W2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="X2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="Y2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="Z2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AA2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AB2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AC2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AD2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AE2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AF2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.15</v>
+        <v>0.14119999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/elec/RM/Reserve Margin.xlsx
+++ b/InputData/elec/RM/Reserve Margin.xlsx
@@ -1,26 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27618"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\RM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robbie\Dropbox (Energy InNovation)\My Documents\Policy Solutions Project\India\India EPS\InputData UPDATE FOR INDIA\elec\RM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_CA1315D1C3942817C980C9C0739AC1F54602E958" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2DE343D-827C-4D02-8B8E-2211F107BF8B}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="75" windowWidth="22995" windowHeight="11580"/>
+    <workbookView xWindow="480" yWindow="75" windowWidth="22995" windowHeight="11580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="RM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>RM Reserve Margin</t>
   </si>
@@ -28,41 +45,26 @@
     <t>Source:</t>
   </si>
   <si>
-    <t xml:space="preserve">North American Electrict Reliability Coorporation </t>
+    <t>NA</t>
   </si>
   <si>
-    <t>http://www.nerc.com/pa/RAPA/ra/Reliability%20Assessments%20DL/2015_Summer_Reliability_Assessment.pdf</t>
+    <t>Notes:</t>
   </si>
   <si>
-    <t>p.3, Table 1: Projected Demand, Resources, and Planning Reserve Margins, NERC Reference Margin Level (%)</t>
+    <t xml:space="preserve">India's actual reserve margin is very high, on the order of 50-70%, so we </t>
   </si>
   <si>
-    <t>2015 Summer Reliability Assessment</t>
+    <t>default to a normal, "good practice" reserve margin of 15%.</t>
   </si>
   <si>
     <t>Reserve Margin</t>
   </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The reserve margin (difference between the total generation available and the forecasted peak demand) in the U.S. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dataset doesn't vary by year, but the RM Reserve Margin variable is a time series to support countries that project </t>
-  </si>
-  <si>
-    <t>changes in future reserve margin by year.</t>
-  </si>
-  <si>
-    <t>(dimensionless)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,13 +101,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -124,9 +125,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,9 +165,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -201,7 +202,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -236,7 +237,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,16 +410,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -426,44 +427,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B4" s="2">
-        <v>2015</v>
-      </c>
+    <row r="4" spans="1:2">
+      <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:2">
+      <c r="B5" s="2"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -473,243 +455,495 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
+    <row r="1" spans="1:51">
       <c r="B1">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C1">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D1">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="E1">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="F1">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="G1">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="H1">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="I1">
-        <v>2022</v>
+        <v>2028</v>
       </c>
       <c r="J1">
-        <v>2023</v>
+        <v>2029</v>
       </c>
       <c r="K1">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="L1">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="M1">
-        <v>2026</v>
+        <v>2032</v>
       </c>
       <c r="N1">
-        <v>2027</v>
+        <v>2033</v>
       </c>
       <c r="O1">
-        <v>2028</v>
+        <v>2034</v>
       </c>
       <c r="P1">
-        <v>2029</v>
+        <v>2035</v>
       </c>
       <c r="Q1">
-        <v>2030</v>
+        <v>2036</v>
       </c>
       <c r="R1">
-        <v>2031</v>
+        <v>2037</v>
       </c>
       <c r="S1">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="T1">
-        <v>2033</v>
+        <v>2039</v>
       </c>
       <c r="U1">
-        <v>2034</v>
+        <v>2040</v>
       </c>
       <c r="V1">
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="W1">
-        <v>2036</v>
+        <v>2042</v>
       </c>
       <c r="X1">
-        <v>2037</v>
+        <v>2043</v>
       </c>
       <c r="Y1">
-        <v>2038</v>
+        <v>2044</v>
       </c>
       <c r="Z1">
-        <v>2039</v>
+        <v>2045</v>
       </c>
       <c r="AA1">
-        <v>2040</v>
+        <v>2046</v>
       </c>
       <c r="AB1">
-        <v>2041</v>
+        <v>2047</v>
       </c>
       <c r="AC1">
-        <v>2042</v>
+        <v>2048</v>
       </c>
       <c r="AD1">
-        <v>2043</v>
+        <v>2049</v>
       </c>
       <c r="AE1">
-        <v>2044</v>
+        <v>2050</v>
       </c>
       <c r="AF1">
-        <v>2045</v>
+        <v>2051</v>
       </c>
       <c r="AG1">
-        <v>2046</v>
+        <v>2052</v>
       </c>
       <c r="AH1">
-        <v>2047</v>
+        <v>2053</v>
       </c>
       <c r="AI1">
-        <v>2048</v>
+        <v>2054</v>
       </c>
       <c r="AJ1">
-        <v>2049</v>
+        <v>2055</v>
       </c>
       <c r="AK1">
-        <v>2050</v>
+        <v>2056</v>
+      </c>
+      <c r="AL1">
+        <v>2057</v>
+      </c>
+      <c r="AM1">
+        <v>2058</v>
+      </c>
+      <c r="AN1">
+        <v>2059</v>
+      </c>
+      <c r="AO1">
+        <v>2060</v>
+      </c>
+      <c r="AP1">
+        <v>2061</v>
+      </c>
+      <c r="AQ1">
+        <v>2062</v>
+      </c>
+      <c r="AR1">
+        <v>2063</v>
+      </c>
+      <c r="AS1">
+        <v>2064</v>
+      </c>
+      <c r="AT1">
+        <v>2065</v>
+      </c>
+      <c r="AU1">
+        <v>2066</v>
+      </c>
+      <c r="AV1">
+        <v>2067</v>
+      </c>
+      <c r="AW1">
+        <v>2068</v>
+      </c>
+      <c r="AX1">
+        <v>2069</v>
+      </c>
+      <c r="AY1">
+        <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:51">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="K2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="O2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="U2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="V2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="X2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AG2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AI2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AJ2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AK2" s="3">
-        <v>0.14119999999999999</v>
+      <c r="B2">
+        <v>0.15</v>
+      </c>
+      <c r="C2">
+        <v>0.15</v>
+      </c>
+      <c r="D2">
+        <v>0.15</v>
+      </c>
+      <c r="E2">
+        <v>0.15</v>
+      </c>
+      <c r="F2">
+        <v>0.15</v>
+      </c>
+      <c r="G2">
+        <v>0.15</v>
+      </c>
+      <c r="H2">
+        <v>0.15</v>
+      </c>
+      <c r="I2">
+        <v>0.15</v>
+      </c>
+      <c r="J2">
+        <v>0.15</v>
+      </c>
+      <c r="K2">
+        <v>0.15</v>
+      </c>
+      <c r="L2">
+        <v>0.15</v>
+      </c>
+      <c r="M2">
+        <v>0.15</v>
+      </c>
+      <c r="N2">
+        <v>0.15</v>
+      </c>
+      <c r="O2">
+        <v>0.15</v>
+      </c>
+      <c r="P2">
+        <v>0.15</v>
+      </c>
+      <c r="Q2">
+        <v>0.15</v>
+      </c>
+      <c r="R2">
+        <v>0.15</v>
+      </c>
+      <c r="S2">
+        <v>0.15</v>
+      </c>
+      <c r="T2">
+        <v>0.15</v>
+      </c>
+      <c r="U2">
+        <v>0.15</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.15</v>
+      </c>
+      <c r="X2">
+        <v>0.15</v>
+      </c>
+      <c r="Y2">
+        <v>0.15</v>
+      </c>
+      <c r="Z2">
+        <v>0.15</v>
+      </c>
+      <c r="AA2">
+        <v>0.15</v>
+      </c>
+      <c r="AB2">
+        <v>0.15</v>
+      </c>
+      <c r="AC2">
+        <v>0.15</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0.15</v>
+      </c>
+      <c r="AF2">
+        <v>0.15</v>
+      </c>
+      <c r="AG2">
+        <v>0.15</v>
+      </c>
+      <c r="AH2">
+        <v>0.15</v>
+      </c>
+      <c r="AI2">
+        <v>0.15</v>
+      </c>
+      <c r="AJ2">
+        <v>0.15</v>
+      </c>
+      <c r="AK2">
+        <v>0.15</v>
+      </c>
+      <c r="AL2">
+        <v>0.15</v>
+      </c>
+      <c r="AM2">
+        <v>0.15</v>
+      </c>
+      <c r="AN2">
+        <v>0.15</v>
+      </c>
+      <c r="AO2">
+        <v>0.15</v>
+      </c>
+      <c r="AP2">
+        <v>0.15</v>
+      </c>
+      <c r="AQ2">
+        <v>0.15</v>
+      </c>
+      <c r="AR2">
+        <v>0.15</v>
+      </c>
+      <c r="AS2">
+        <v>0.15</v>
+      </c>
+      <c r="AT2">
+        <v>0.15</v>
+      </c>
+      <c r="AU2">
+        <v>0.15</v>
+      </c>
+      <c r="AV2">
+        <v>0.15</v>
+      </c>
+      <c r="AW2">
+        <v>0.15</v>
+      </c>
+      <c r="AX2">
+        <v>0.15</v>
+      </c>
+      <c r="AY2">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{363012C4-49C3-4B16-9D34-C8DF2042680D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9DC02AA-3C9E-4443-AAD1-601966C2C259}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F66FBC20-510F-45BE-8789-6FC24AD5533C}"/>
 </file>